--- a/15-11-2025 HMS-TAX/HMS-TAX/bin/Debug/Reports/rpt_po_details.xlsx
+++ b/15-11-2025 HMS-TAX/HMS-TAX/bin/Debug/Reports/rpt_po_details.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16770"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="29040" windowHeight="16440"/>
   </bookViews>
   <sheets>
     <sheet name="PO" sheetId="1" r:id="rId1"/>
@@ -49,9 +49,6 @@
     <t>Exp</t>
   </si>
   <si>
-    <t>Purchase Order detail</t>
-  </si>
-  <si>
     <t>PO ID</t>
   </si>
   <si>
@@ -62,6 +59,9 @@
   </si>
   <si>
     <t>Expired Date</t>
+  </si>
+  <si>
+    <t>Purchase Order details</t>
   </si>
 </sst>
 </file>
@@ -253,15 +253,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -593,7 +593,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
-      <c r="I1" s="31"/>
+      <c r="I1" s="29"/>
       <c r="J1" s="24"/>
       <c r="K1" s="18"/>
       <c r="L1" s="1"/>
@@ -602,18 +602,18 @@
     </row>
     <row r="2" spans="2:16" customFormat="1" ht="13.15" customHeight="1">
       <c r="B2" s="21"/>
-      <c r="C2" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
+      <c r="C2" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
       <c r="M2" s="28"/>
       <c r="N2" s="16"/>
       <c r="O2" s="2"/>
@@ -621,16 +621,16 @@
     </row>
     <row r="3" spans="2:16" customFormat="1" ht="16.899999999999999" customHeight="1">
       <c r="B3" s="21"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
       <c r="M3" s="28"/>
       <c r="N3" s="16"/>
       <c r="O3" s="2"/>
@@ -641,14 +641,14 @@
       <c r="C4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="32">
         <v>42285</v>
       </c>
-      <c r="E4" s="30"/>
+      <c r="E4" s="32"/>
       <c r="F4" s="9"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
-      <c r="I4" s="32"/>
+      <c r="I4" s="30"/>
       <c r="J4" s="25"/>
       <c r="K4" s="19"/>
       <c r="L4" s="3"/>
@@ -660,13 +660,13 @@
         <v>0</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>9</v>
@@ -690,13 +690,13 @@
         <v>3</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N5" s="13" t="s">
         <v>6</v>
       </c>
       <c r="O5" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
